--- a/addons/account/static/xls/vendor_bills_refunds_import_template.xlsx
+++ b/addons/account/static/xls/vendor_bills_refunds_import_template.xlsx
@@ -85,7 +85,7 @@
     <t xml:space="preserve">Desk Pad</t>
   </si>
   <si>
-    <t xml:space="preserve">Deco Addict</t>
+    <t xml:space="preserve">Acme Corporation</t>
   </si>
   <si>
     <t xml:space="preserve">REF161800</t>
